--- a/data/latest_data.xlsx
+++ b/data/latest_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\고객센터 평가\2026년 09월\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\고객센터 평가\2026년 08월\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{770F57D6-AF2D-49B6-87FC-4CA0CF4C65A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3727B73D-E865-484C-9263-03272921B037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{374363BE-A5F5-4ADC-8A41-9D43B010FE25}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{374363BE-A5F5-4ADC-8A41-9D43B010FE25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="41">
   <si>
     <t>센터명</t>
   </si>
@@ -167,7 +167,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -653,13 +653,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576B49EF-D72C-489F-81B1-8DBFDE47B864}">
-  <dimension ref="A1:L505"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:L482"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="11" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="62.25" customHeight="1" thickBot="1">
+    <row r="1" spans="1:12" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +697,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="2" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>11</v>
       </c>
@@ -733,7 +733,7 @@
         <v>447.95</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="3" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>12</v>
       </c>
@@ -769,7 +769,7 @@
         <v>444.4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="4" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>13</v>
       </c>
@@ -805,7 +805,7 @@
         <v>412.19</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="5" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>14</v>
       </c>
@@ -841,7 +841,7 @@
         <v>505.92</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="6" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>15</v>
       </c>
@@ -877,7 +877,7 @@
         <v>469.07</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="7" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>16</v>
       </c>
@@ -913,7 +913,7 @@
         <v>462.9</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="8" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
@@ -949,7 +949,7 @@
         <v>482.45</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="9" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>18</v>
       </c>
@@ -985,7 +985,7 @@
         <v>469.48</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="10" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>19</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>452.91</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="11" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>20</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>470.93</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="12" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>21</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>457.46</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="13" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>22</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>480.39</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="14" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>478.09</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="15" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>24</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>482.12</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="16" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>37</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>508.53</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="17" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>26</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>480.66</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="18" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>27</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>443.39</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="19" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>28</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>492.5</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="20" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>29</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>441.26</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="21" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>30</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>464.06</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="22" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>31</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>486.83</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="23" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>32</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>430.67</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="24" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>38</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>387.78</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="25" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>39</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>438.64</v>
       </c>
     </row>
-    <row r="26" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="26" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
         <v>34</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>471.85</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="27" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
         <v>40</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>448.63</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="28" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
         <v>11</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>576.36</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="29" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
         <v>12</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>540.49</v>
       </c>
     </row>
-    <row r="30" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="30" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
         <v>13</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>551.99</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="31" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
         <v>14</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>624.82000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="32" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
         <v>15</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>590.49</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="33" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>16</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>591.23</v>
       </c>
     </row>
-    <row r="34" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="34" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
         <v>17</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>583.07000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="35" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
         <v>18</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>589.19000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="36" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
         <v>19</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>550.09</v>
       </c>
     </row>
-    <row r="37" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="37" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
         <v>20</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>592.29999999999995</v>
       </c>
     </row>
-    <row r="38" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="38" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
         <v>21</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>590.25</v>
       </c>
     </row>
-    <row r="39" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="39" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>22</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>583.16999999999996</v>
       </c>
     </row>
-    <row r="40" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="40" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>23</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>610.48</v>
       </c>
     </row>
-    <row r="41" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="41" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
         <v>24</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>586.91</v>
       </c>
     </row>
-    <row r="42" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="42" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
         <v>37</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>649.12</v>
       </c>
     </row>
-    <row r="43" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="43" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
         <v>26</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>588.14</v>
       </c>
     </row>
-    <row r="44" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="44" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
         <v>27</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>583.84</v>
       </c>
     </row>
-    <row r="45" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="45" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>28</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>602.25</v>
       </c>
     </row>
-    <row r="46" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="46" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
         <v>29</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>559.08000000000004</v>
       </c>
     </row>
-    <row r="47" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="47" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
         <v>30</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>595.77</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="48" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
         <v>31</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>602.34</v>
       </c>
     </row>
-    <row r="49" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="49" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
         <v>32</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>547.1</v>
       </c>
     </row>
-    <row r="50" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="50" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
         <v>38</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>503.26</v>
       </c>
     </row>
-    <row r="51" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="51" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
         <v>39</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>548.6</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="52" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
         <v>34</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>540.01</v>
       </c>
     </row>
-    <row r="53" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="53" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
         <v>40</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>587.36</v>
       </c>
     </row>
-    <row r="54" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="54" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
         <v>11</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>720.03</v>
       </c>
     </row>
-    <row r="55" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="55" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
         <v>12</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>645.54999999999995</v>
       </c>
     </row>
-    <row r="56" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="56" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
         <v>13</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>653.84</v>
       </c>
     </row>
-    <row r="57" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="57" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
         <v>14</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>746.24</v>
       </c>
     </row>
-    <row r="58" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="58" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
         <v>15</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>713.51</v>
       </c>
     </row>
-    <row r="59" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="59" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
         <v>16</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>728.67</v>
       </c>
     </row>
-    <row r="60" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="60" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
         <v>17</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>670.76</v>
       </c>
     </row>
-    <row r="61" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="61" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
         <v>18</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>695.55</v>
       </c>
     </row>
-    <row r="62" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="62" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="9" t="s">
         <v>19</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>664.69</v>
       </c>
     </row>
-    <row r="63" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="63" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
         <v>20</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>708.07</v>
       </c>
     </row>
-    <row r="64" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="64" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="9" t="s">
         <v>21</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>719.76</v>
       </c>
     </row>
-    <row r="65" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="65" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
         <v>22</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>697.09</v>
       </c>
     </row>
-    <row r="66" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="66" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
         <v>23</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>706.33</v>
       </c>
     </row>
-    <row r="67" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="67" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
         <v>24</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>693.85</v>
       </c>
     </row>
-    <row r="68" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="68" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
         <v>37</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>741.48</v>
       </c>
     </row>
-    <row r="69" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="69" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
         <v>26</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>681.7</v>
       </c>
     </row>
-    <row r="70" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="70" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="9" t="s">
         <v>27</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>695.22</v>
       </c>
     </row>
-    <row r="71" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="71" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
         <v>28</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>710.3</v>
       </c>
     </row>
-    <row r="72" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="72" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9" t="s">
         <v>29</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>671.03</v>
       </c>
     </row>
-    <row r="73" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="73" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9" t="s">
         <v>30</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>722.04</v>
       </c>
     </row>
-    <row r="74" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="74" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
         <v>31</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>721.93</v>
       </c>
     </row>
-    <row r="75" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="75" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="9" t="s">
         <v>32</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="76" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="76" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="9" t="s">
         <v>38</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>596.29999999999995</v>
       </c>
     </row>
-    <row r="77" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="77" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="9" t="s">
         <v>39</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>626.44000000000005</v>
       </c>
     </row>
-    <row r="78" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="78" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9" t="s">
         <v>34</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>637.66999999999996</v>
       </c>
     </row>
-    <row r="79" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="79" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="9" t="s">
         <v>40</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>708.09</v>
       </c>
     </row>
-    <row r="80" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="80" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="9" t="s">
         <v>11</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>847.19</v>
       </c>
     </row>
-    <row r="81" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="81" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="9" t="s">
         <v>12</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>790.45</v>
       </c>
     </row>
-    <row r="82" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="82" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="9" t="s">
         <v>13</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>774.73</v>
       </c>
     </row>
-    <row r="83" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="83" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9" t="s">
         <v>14</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>876.06</v>
       </c>
     </row>
-    <row r="84" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="84" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="9" t="s">
         <v>15</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>827.07</v>
       </c>
     </row>
-    <row r="85" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="85" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="9" t="s">
         <v>16</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>853.54</v>
       </c>
     </row>
-    <row r="86" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="86" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="9" t="s">
         <v>17</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>763.19</v>
       </c>
     </row>
-    <row r="87" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="87" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="9" t="s">
         <v>18</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>802.8</v>
       </c>
     </row>
-    <row r="88" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="88" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="9" t="s">
         <v>19</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>797.01</v>
       </c>
     </row>
-    <row r="89" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="89" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="9" t="s">
         <v>20</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>819.8</v>
       </c>
     </row>
-    <row r="90" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="90" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="9" t="s">
         <v>21</v>
       </c>
@@ -3901,7 +3901,7 @@
         <v>829.57</v>
       </c>
     </row>
-    <row r="91" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="91" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9" t="s">
         <v>22</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>816.61</v>
       </c>
     </row>
-    <row r="92" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="92" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="9" t="s">
         <v>23</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>799.18</v>
       </c>
     </row>
-    <row r="93" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="93" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="9" t="s">
         <v>24</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>812.91</v>
       </c>
     </row>
-    <row r="94" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="94" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="9" t="s">
         <v>25</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>750.8</v>
       </c>
     </row>
-    <row r="95" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="95" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="9" t="s">
         <v>26</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>779.46</v>
       </c>
     </row>
-    <row r="96" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="96" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="9" t="s">
         <v>27</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>810.93</v>
       </c>
     </row>
-    <row r="97" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="97" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="9" t="s">
         <v>28</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>821.8</v>
       </c>
     </row>
-    <row r="98" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="98" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="9" t="s">
         <v>29</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>779.39</v>
       </c>
     </row>
-    <row r="99" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="99" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="9" t="s">
         <v>30</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>845.37</v>
       </c>
     </row>
-    <row r="100" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="100" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="9" t="s">
         <v>31</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>842.81</v>
       </c>
     </row>
-    <row r="101" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="101" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="9" t="s">
         <v>32</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>777.68</v>
       </c>
     </row>
-    <row r="102" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="102" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="9" t="s">
         <v>33</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>797.54</v>
       </c>
     </row>
-    <row r="103" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="103" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="9" t="s">
         <v>34</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>745.61</v>
       </c>
     </row>
-    <row r="104" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="104" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="9" t="s">
         <v>11</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>926.64</v>
       </c>
     </row>
-    <row r="105" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="105" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="9" t="s">
         <v>12</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>896.64</v>
       </c>
     </row>
-    <row r="106" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="106" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="9" t="s">
         <v>13</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>877.43</v>
       </c>
     </row>
-    <row r="107" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="107" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="9" t="s">
         <v>14</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>960.92</v>
       </c>
     </row>
-    <row r="108" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="108" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="9" t="s">
         <v>15</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>918.05</v>
       </c>
     </row>
-    <row r="109" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="109" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="9" t="s">
         <v>16</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>937.9</v>
       </c>
     </row>
-    <row r="110" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="110" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="9" t="s">
         <v>17</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>849.79</v>
       </c>
     </row>
-    <row r="111" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="111" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="9" t="s">
         <v>18</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>909.6</v>
       </c>
     </row>
-    <row r="112" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="112" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="9" t="s">
         <v>19</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>889.2</v>
       </c>
     </row>
-    <row r="113" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="113" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="9" t="s">
         <v>20</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>904.6</v>
       </c>
     </row>
-    <row r="114" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="114" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="9" t="s">
         <v>21</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>911.33</v>
       </c>
     </row>
-    <row r="115" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="115" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="9" t="s">
         <v>22</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>908.11</v>
       </c>
     </row>
-    <row r="116" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="116" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="9" t="s">
         <v>23</v>
       </c>
@@ -4837,7 +4837,7 @@
         <v>906.39</v>
       </c>
     </row>
-    <row r="117" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="117" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="9" t="s">
         <v>24</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>916.28</v>
       </c>
     </row>
-    <row r="118" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="118" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="9" t="s">
         <v>25</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>804.77</v>
       </c>
     </row>
-    <row r="119" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="119" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="9" t="s">
         <v>26</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>876.92</v>
       </c>
     </row>
-    <row r="120" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="120" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="9" t="s">
         <v>27</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>925.77</v>
       </c>
     </row>
-    <row r="121" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="121" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="9" t="s">
         <v>28</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>912.03</v>
       </c>
     </row>
-    <row r="122" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="122" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="9" t="s">
         <v>29</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>884.72</v>
       </c>
     </row>
-    <row r="123" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="123" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="9" t="s">
         <v>30</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>928.49</v>
       </c>
     </row>
-    <row r="124" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="124" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="9" t="s">
         <v>31</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>932.32</v>
       </c>
     </row>
-    <row r="125" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="125" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="9" t="s">
         <v>32</v>
       </c>
@@ -5161,7 +5161,7 @@
         <v>857.82</v>
       </c>
     </row>
-    <row r="126" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="126" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="9" t="s">
         <v>33</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>901.7</v>
       </c>
     </row>
-    <row r="127" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="127" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="9" t="s">
         <v>34</v>
       </c>
@@ -5233,7 +5233,7 @@
         <v>865.68</v>
       </c>
     </row>
-    <row r="128" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="128" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="9" t="s">
         <v>11</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>958.83</v>
       </c>
     </row>
-    <row r="129" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="129" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="9" t="s">
         <v>12</v>
       </c>
@@ -5305,7 +5305,7 @@
         <v>950.59</v>
       </c>
     </row>
-    <row r="130" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="130" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="9" t="s">
         <v>13</v>
       </c>
@@ -5341,7 +5341,7 @@
         <v>936.16</v>
       </c>
     </row>
-    <row r="131" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="131" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="9" t="s">
         <v>14</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>966.68</v>
       </c>
     </row>
-    <row r="132" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="132" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="9" t="s">
         <v>15</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>942.8</v>
       </c>
     </row>
-    <row r="133" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="133" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="9" t="s">
         <v>16</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>958.82</v>
       </c>
     </row>
-    <row r="134" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="134" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="9" t="s">
         <v>17</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>925.51</v>
       </c>
     </row>
-    <row r="135" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="135" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="9" t="s">
         <v>18</v>
       </c>
@@ -5521,7 +5521,7 @@
         <v>958.66</v>
       </c>
     </row>
-    <row r="136" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="136" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="9" t="s">
         <v>19</v>
       </c>
@@ -5557,7 +5557,7 @@
         <v>931.1</v>
       </c>
     </row>
-    <row r="137" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="137" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="9" t="s">
         <v>20</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>942.59</v>
       </c>
     </row>
-    <row r="138" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="138" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="9" t="s">
         <v>21</v>
       </c>
@@ -5629,7 +5629,7 @@
         <v>934.05</v>
       </c>
     </row>
-    <row r="139" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="139" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="9" t="s">
         <v>22</v>
       </c>
@@ -5665,7 +5665,7 @@
         <v>940.14</v>
       </c>
     </row>
-    <row r="140" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="140" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="9" t="s">
         <v>23</v>
       </c>
@@ -5701,7 +5701,7 @@
         <v>943.38</v>
       </c>
     </row>
-    <row r="141" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="141" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="9" t="s">
         <v>24</v>
       </c>
@@ -5737,7 +5737,7 @@
         <v>944.57</v>
       </c>
     </row>
-    <row r="142" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="142" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="9" t="s">
         <v>25</v>
       </c>
@@ -5773,7 +5773,7 @@
         <v>846.12</v>
       </c>
     </row>
-    <row r="143" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="143" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="9" t="s">
         <v>26</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>932.52</v>
       </c>
     </row>
-    <row r="144" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="144" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="9" t="s">
         <v>27</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>964.27</v>
       </c>
     </row>
-    <row r="145" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="145" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="9" t="s">
         <v>28</v>
       </c>
@@ -5881,7 +5881,7 @@
         <v>940.76</v>
       </c>
     </row>
-    <row r="146" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="146" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="9" t="s">
         <v>29</v>
       </c>
@@ -5917,7 +5917,7 @@
         <v>944.32</v>
       </c>
     </row>
-    <row r="147" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="147" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="9" t="s">
         <v>30</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>941.27</v>
       </c>
     </row>
-    <row r="148" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="148" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="9" t="s">
         <v>31</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>941.52</v>
       </c>
     </row>
-    <row r="149" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="149" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="9" t="s">
         <v>32</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>902.91</v>
       </c>
     </row>
-    <row r="150" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="150" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="9" t="s">
         <v>33</v>
       </c>
@@ -6061,7 +6061,7 @@
         <v>940.11</v>
       </c>
     </row>
-    <row r="151" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="151" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="9" t="s">
         <v>34</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>917.25</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="21.75" thickBot="1">
+    <row r="152" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>11</v>
       </c>
@@ -6133,7 +6133,7 @@
         <v>483.63001902191979</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="21.75" thickBot="1">
+    <row r="153" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>12</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>471.9796990831025</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="21.75" thickBot="1">
+    <row r="154" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>13</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>493.76845693808036</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="21.75" thickBot="1">
+    <row r="155" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>14</v>
       </c>
@@ -6241,7 +6241,7 @@
         <v>505.17702686522352</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="21.75" thickBot="1">
+    <row r="156" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>15</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>488.05229391161532</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="21.75" thickBot="1">
+    <row r="157" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>16</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>520.8745525512129</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="21.75" thickBot="1">
+    <row r="158" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>17</v>
       </c>
@@ -6349,7 +6349,7 @@
         <v>482.6260545655756</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="21.75" thickBot="1">
+    <row r="159" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>18</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>483.44866897598428</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="21.75" thickBot="1">
+    <row r="160" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>19</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>463.37401636560901</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="21.75" thickBot="1">
+    <row r="161" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>20</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>527.36573327814097</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="21.75" thickBot="1">
+    <row r="162" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>21</v>
       </c>
@@ -6493,7 +6493,7 @@
         <v>515.63571631679781</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="21.75" thickBot="1">
+    <row r="163" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>22</v>
       </c>
@@ -6529,7 +6529,7 @@
         <v>490.99777323219564</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="21.75" thickBot="1">
+    <row r="164" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>23</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>446.88900930385239</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="21.75" thickBot="1">
+    <row r="165" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>24</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>516.32306575075438</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="21.75" thickBot="1">
+    <row r="166" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>25</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>412.33102076373655</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="21.75" thickBot="1">
+    <row r="167" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>26</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>530.54058798167034</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="21.75" thickBot="1">
+    <row r="168" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>27</v>
       </c>
@@ -6709,7 +6709,7 @@
         <v>439.08852618084654</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="21.75" thickBot="1">
+    <row r="169" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>28</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>500.48997040580167</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="21.75" thickBot="1">
+    <row r="170" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>29</v>
       </c>
@@ -6781,7 +6781,7 @@
         <v>512.46176309442455</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="21.75" thickBot="1">
+    <row r="171" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>30</v>
       </c>
@@ -6817,7 +6817,7 @@
         <v>464.00633033002453</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="21.75" thickBot="1">
+    <row r="172" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>31</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>516.3115256865301</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="21.75" thickBot="1">
+    <row r="173" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>32</v>
       </c>
@@ -6889,7 +6889,7 @@
         <v>470.62928714951721</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="21.75" thickBot="1">
+    <row r="174" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>33</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>499.16205129454488</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="21.75" thickBot="1">
+    <row r="175" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>34</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>504.83348314853424</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="21.75" thickBot="1">
+    <row r="176" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>11</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>623.93126800884113</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="21.75" thickBot="1">
+    <row r="177" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>12</v>
       </c>
@@ -7033,7 +7033,7 @@
         <v>585.88936431567515</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="21.75" thickBot="1">
+    <row r="178" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>13</v>
       </c>
@@ -7069,7 +7069,7 @@
         <v>599.14650713811</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="21.75" thickBot="1">
+    <row r="179" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>14</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>620.5441128156906</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="21.75" thickBot="1">
+    <row r="180" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>15</v>
       </c>
@@ -7141,7 +7141,7 @@
         <v>657.14176878262867</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="21.75" thickBot="1">
+    <row r="181" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>16</v>
       </c>
@@ -7177,7 +7177,7 @@
         <v>640.61662648535594</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="21.75" thickBot="1">
+    <row r="182" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>17</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>575.59373626367528</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="21.75" thickBot="1">
+    <row r="183" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>18</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>583.01963694765857</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="21.75" thickBot="1">
+    <row r="184" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>19</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>578.03440122043253</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="21.75" thickBot="1">
+    <row r="185" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>20</v>
       </c>
@@ -7321,7 +7321,7 @@
         <v>640.96150707127674</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="21.75" thickBot="1">
+    <row r="186" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>21</v>
       </c>
@@ -7357,7 +7357,7 @@
         <v>649.58255784712651</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="21.75" thickBot="1">
+    <row r="187" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>22</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>589.5156879808651</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="21.75" thickBot="1">
+    <row r="188" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>23</v>
       </c>
@@ -7429,7 +7429,7 @@
         <v>565.81176631722713</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="21.75" thickBot="1">
+    <row r="189" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>24</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>634.44350804786359</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="21.75" thickBot="1">
+    <row r="190" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>25</v>
       </c>
@@ -7501,7 +7501,7 @@
         <v>532.10117969280975</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="21.75" thickBot="1">
+    <row r="191" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>26</v>
       </c>
@@ -7537,7 +7537,7 @@
         <v>627.31478847249161</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="21.75" thickBot="1">
+    <row r="192" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>27</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>570.05862720524146</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="21.75" thickBot="1">
+    <row r="193" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>28</v>
       </c>
@@ -7609,7 +7609,7 @@
         <v>607.32960172126786</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="21.75" thickBot="1">
+    <row r="194" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>29</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>620.26497673244535</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="21.75" thickBot="1">
+    <row r="195" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>30</v>
       </c>
@@ -7681,7 +7681,7 @@
         <v>576.89532108296521</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="21.75" thickBot="1">
+    <row r="196" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>31</v>
       </c>
@@ -7717,7 +7717,7 @@
         <v>626.57278038321726</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="21.75" thickBot="1">
+    <row r="197" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>32</v>
       </c>
@@ -7753,7 +7753,7 @@
         <v>615.97121499767388</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="21.75" thickBot="1">
+    <row r="198" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>33</v>
       </c>
@@ -7789,7 +7789,7 @@
         <v>602.10386083698143</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="21.75" thickBot="1">
+    <row r="199" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>34</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>617.14079294282305</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="21.75" thickBot="1">
+    <row r="200" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>11</v>
       </c>
@@ -7861,7 +7861,7 @@
         <v>739.17463411421409</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="21.75" thickBot="1">
+    <row r="201" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>12</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>726.63754183191884</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="21.75" thickBot="1">
+    <row r="202" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>13</v>
       </c>
@@ -7933,7 +7933,7 @@
         <v>707.59592728440305</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="21.75" thickBot="1">
+    <row r="203" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>14</v>
       </c>
@@ -7969,7 +7969,7 @@
         <v>726.25076670268152</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="21.75" thickBot="1">
+    <row r="204" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>15</v>
       </c>
@@ -8005,7 +8005,7 @@
         <v>756.01515863168026</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="21.75" thickBot="1">
+    <row r="205" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>16</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>772.13008928168585</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="21.75" thickBot="1">
+    <row r="206" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>17</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>670.62439587616518</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="21.75" thickBot="1">
+    <row r="207" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>18</v>
       </c>
@@ -8113,7 +8113,7 @@
         <v>680.7589784175716</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="21.75" thickBot="1">
+    <row r="208" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>19</v>
       </c>
@@ -8149,7 +8149,7 @@
         <v>691.02234479484343</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="21.75" thickBot="1">
+    <row r="209" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>20</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>749.76099639489394</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="21.75" thickBot="1">
+    <row r="210" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>21</v>
       </c>
@@ -8221,7 +8221,7 @@
         <v>773.87566054714489</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="21.75" thickBot="1">
+    <row r="211" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>22</v>
       </c>
@@ -8257,7 +8257,7 @@
         <v>698.52656448933885</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="21.75" thickBot="1">
+    <row r="212" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>23</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>694.68294760559388</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="21.75" thickBot="1">
+    <row r="213" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>24</v>
       </c>
@@ -8329,7 +8329,7 @@
         <v>736.80934106449718</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="21.75" thickBot="1">
+    <row r="214" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>25</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>659.3267753002466</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="21.75" thickBot="1">
+    <row r="215" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>26</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>724.85311946859417</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="21.75" thickBot="1">
+    <row r="216" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>27</v>
       </c>
@@ -8437,7 +8437,7 @@
         <v>686.46136514010027</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="21.75" thickBot="1">
+    <row r="217" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>28</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>722.5310433310741</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="21.75" thickBot="1">
+    <row r="218" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>29</v>
       </c>
@@ -8509,7 +8509,7 @@
         <v>718.07660014532701</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="21.75" thickBot="1">
+    <row r="219" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>30</v>
       </c>
@@ -8545,7 +8545,7 @@
         <v>713.19496400983553</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="21.75" thickBot="1">
+    <row r="220" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>31</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>756.60830674684553</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="21.75" thickBot="1">
+    <row r="221" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>32</v>
       </c>
@@ -8617,7 +8617,7 @@
         <v>728.14885040968989</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="21.75" thickBot="1">
+    <row r="222" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>33</v>
       </c>
@@ -8653,7 +8653,7 @@
         <v>704.67554761818042</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="21.75" thickBot="1">
+    <row r="223" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>34</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>727.48627103847207</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="21.75" thickBot="1">
+    <row r="224" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>11</v>
       </c>
@@ -8725,7 +8725,7 @@
         <v>838.93767803920025</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="21.75" thickBot="1">
+    <row r="225" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>12</v>
       </c>
@@ -8761,7 +8761,7 @@
         <v>816.87605298733422</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="21.75" thickBot="1">
+    <row r="226" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>13</v>
       </c>
@@ -8797,7 +8797,7 @@
         <v>787.10902937873368</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="21.75" thickBot="1">
+    <row r="227" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>14</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>829.21581353796182</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="21.75" thickBot="1">
+    <row r="228" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>15</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>835.69496551736972</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="21.75" thickBot="1">
+    <row r="229" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>16</v>
       </c>
@@ -8905,7 +8905,7 @@
         <v>872.98008298190302</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="21.75" thickBot="1">
+    <row r="230" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>17</v>
       </c>
@@ -8941,7 +8941,7 @@
         <v>748.63789713579547</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="21.75" thickBot="1">
+    <row r="231" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>18</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>770.25065608750231</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="21.75" thickBot="1">
+    <row r="232" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>19</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>776.51072357128066</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="21.75" thickBot="1">
+    <row r="233" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>20</v>
       </c>
@@ -9049,7 +9049,7 @@
         <v>831.59239781856832</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="21.75" thickBot="1">
+    <row r="234" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>21</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>862.07114425813052</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="21.75" thickBot="1">
+    <row r="235" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>22</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>787.95076007947523</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="21.75" thickBot="1">
+    <row r="236" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>23</v>
       </c>
@@ -9157,7 +9157,7 @@
         <v>780.37433796458242</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="21.75" thickBot="1">
+    <row r="237" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>24</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>817.11187746523888</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="21.75" thickBot="1">
+    <row r="238" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>25</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>735.84118054471321</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="21.75" thickBot="1">
+    <row r="239" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>26</v>
       </c>
@@ -9265,7 +9265,7 @@
         <v>799.04387764495959</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="21.75" thickBot="1">
+    <row r="240" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>27</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>777.20510403562253</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="21.75" thickBot="1">
+    <row r="241" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>28</v>
       </c>
@@ -9337,7 +9337,7 @@
         <v>822.12875098965128</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="21.75" thickBot="1">
+    <row r="242" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>29</v>
       </c>
@@ -9373,7 +9373,7 @@
         <v>802.36942483715211</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="21.75" thickBot="1">
+    <row r="243" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>30</v>
       </c>
@@ -9409,7 +9409,7 @@
         <v>821.80852734610824</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="21.75" thickBot="1">
+    <row r="244" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>31</v>
       </c>
@@ -9445,7 +9445,7 @@
         <v>841.10577803493777</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="21.75" thickBot="1">
+    <row r="245" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>32</v>
       </c>
@@ -9481,7 +9481,7 @@
         <v>780.84407184475742</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="21.75" thickBot="1">
+    <row r="246" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>33</v>
       </c>
@@ -9517,7 +9517,7 @@
         <v>817.05445513027166</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="21.75" thickBot="1">
+    <row r="247" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>34</v>
       </c>
@@ -9553,7 +9553,7 @@
         <v>799.32852242927163</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="21.75" thickBot="1">
+    <row r="248" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A248" s="5" t="s">
         <v>11</v>
       </c>
@@ -9589,7 +9589,7 @@
         <v>914.13029946191386</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="21.75" thickBot="1">
+    <row r="249" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>12</v>
       </c>
@@ -9625,7 +9625,7 @@
         <v>908.71987830441822</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="21.75" thickBot="1">
+    <row r="250" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>13</v>
       </c>
@@ -9661,7 +9661,7 @@
         <v>868.58215232277234</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="21.75" thickBot="1">
+    <row r="251" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>14</v>
       </c>
@@ -9697,7 +9697,7 @@
         <v>920.86762214718829</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="21.75" thickBot="1">
+    <row r="252" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>15</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>917.66644207350328</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="21.75" thickBot="1">
+    <row r="253" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>16</v>
       </c>
@@ -9769,7 +9769,7 @@
         <v>947.03927099760233</v>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="21.75" thickBot="1">
+    <row r="254" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>17</v>
       </c>
@@ -9805,7 +9805,7 @@
         <v>849.78552043637433</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="21.75" thickBot="1">
+    <row r="255" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>18</v>
       </c>
@@ -9841,7 +9841,7 @@
         <v>873.98693399465913</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="21.75" thickBot="1">
+    <row r="256" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>19</v>
       </c>
@@ -9877,7 +9877,7 @@
         <v>869.09819890424671</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="21.75" thickBot="1">
+    <row r="257" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>20</v>
       </c>
@@ -9913,7 +9913,7 @@
         <v>917.01199294206515</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="21.75" thickBot="1">
+    <row r="258" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>21</v>
       </c>
@@ -9949,7 +9949,7 @@
         <v>924.3444437695332</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="21.75" thickBot="1">
+    <row r="259" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>22</v>
       </c>
@@ -9985,7 +9985,7 @@
         <v>896.85108529719355</v>
       </c>
     </row>
-    <row r="260" spans="1:12" ht="21.75" thickBot="1">
+    <row r="260" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>23</v>
       </c>
@@ -10021,7 +10021,7 @@
         <v>857.78200601250126</v>
       </c>
     </row>
-    <row r="261" spans="1:12" ht="21.75" thickBot="1">
+    <row r="261" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>24</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>909.77796546576621</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="21.75" thickBot="1">
+    <row r="262" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>25</v>
       </c>
@@ -10093,7 +10093,7 @@
         <v>794.12467521115502</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="21.75" thickBot="1">
+    <row r="263" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>26</v>
       </c>
@@ -10129,7 +10129,7 @@
         <v>878.02296154766645</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="21.75" thickBot="1">
+    <row r="264" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>27</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>897.49535731029255</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="21.75" thickBot="1">
+    <row r="265" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>28</v>
       </c>
@@ -10201,7 +10201,7 @@
         <v>901.2663218986479</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="21.75" thickBot="1">
+    <row r="266" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>29</v>
       </c>
@@ -10237,7 +10237,7 @@
         <v>896.52844601606182</v>
       </c>
     </row>
-    <row r="267" spans="1:12" ht="21.75" thickBot="1">
+    <row r="267" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>30</v>
       </c>
@@ -10273,7 +10273,7 @@
         <v>919.07536277142231</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="21.75" thickBot="1">
+    <row r="268" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>31</v>
       </c>
@@ -10309,7 +10309,7 @@
         <v>918.95680013855895</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="21.75" thickBot="1">
+    <row r="269" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>32</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>845.95633097618429</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="21.75" thickBot="1">
+    <row r="270" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>33</v>
       </c>
@@ -10381,7 +10381,7 @@
         <v>893.93640191039287</v>
       </c>
     </row>
-    <row r="271" spans="1:12" ht="21.75" thickBot="1">
+    <row r="271" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>34</v>
       </c>
@@ -10417,7 +10417,7 @@
         <v>898.62656885178194</v>
       </c>
     </row>
-    <row r="272" spans="1:12" ht="21.75" thickBot="1">
+    <row r="272" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>11</v>
       </c>
@@ -10453,7 +10453,7 @@
         <v>946.44365979685961</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="21.75" thickBot="1">
+    <row r="273" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>12</v>
       </c>
@@ -10489,7 +10489,7 @@
         <v>939.50663628572124</v>
       </c>
     </row>
-    <row r="274" spans="1:12" ht="21.75" thickBot="1">
+    <row r="274" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>13</v>
       </c>
@@ -10525,7 +10525,7 @@
         <v>919.98078120576577</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="21.75" thickBot="1">
+    <row r="275" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>14</v>
       </c>
@@ -10561,7 +10561,7 @@
         <v>944.10883007705331</v>
       </c>
     </row>
-    <row r="276" spans="1:12" ht="21.75" thickBot="1">
+    <row r="276" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>15</v>
       </c>
@@ -10597,7 +10597,7 @@
         <v>928.65468596886126</v>
       </c>
     </row>
-    <row r="277" spans="1:12" ht="21.75" thickBot="1">
+    <row r="277" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>16</v>
       </c>
@@ -10633,7 +10633,7 @@
         <v>961.03201426828412</v>
       </c>
     </row>
-    <row r="278" spans="1:12" ht="21.75" thickBot="1">
+    <row r="278" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>17</v>
       </c>
@@ -10669,7 +10669,7 @@
         <v>929.80445991295312</v>
       </c>
     </row>
-    <row r="279" spans="1:12" ht="21.75" thickBot="1">
+    <row r="279" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>18</v>
       </c>
@@ -10705,7 +10705,7 @@
         <v>935.27800040028069</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="21.75" thickBot="1">
+    <row r="280" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>19</v>
       </c>
@@ -10741,7 +10741,7 @@
         <v>913.09446440964427</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="21.75" thickBot="1">
+    <row r="281" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>20</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>950.86890413045228</v>
       </c>
     </row>
-    <row r="282" spans="1:12" ht="21.75" thickBot="1">
+    <row r="282" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>21</v>
       </c>
@@ -10813,7 +10813,7 @@
         <v>939.53871997339922</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="21.75" thickBot="1">
+    <row r="283" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>22</v>
       </c>
@@ -10849,7 +10849,7 @@
         <v>934.59101043727139</v>
       </c>
     </row>
-    <row r="284" spans="1:12" ht="21.75" thickBot="1">
+    <row r="284" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>23</v>
       </c>
@@ -10885,7 +10885,7 @@
         <v>922.03358742934324</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="21.75" thickBot="1">
+    <row r="285" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>24</v>
       </c>
@@ -10921,7 +10921,7 @@
         <v>938.70606870179677</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="21.75" thickBot="1">
+    <row r="286" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>25</v>
       </c>
@@ -10957,7 +10957,7 @@
         <v>840.93526359503846</v>
       </c>
     </row>
-    <row r="287" spans="1:12" ht="21.75" thickBot="1">
+    <row r="287" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>26</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>929.38411549289424</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="21.75" thickBot="1">
+    <row r="288" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>27</v>
       </c>
@@ -11029,7 +11029,7 @@
         <v>947.41600915552249</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="21.75" thickBot="1">
+    <row r="289" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>28</v>
       </c>
@@ -11065,7 +11065,7 @@
         <v>923.71560049516734</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="21.75" thickBot="1">
+    <row r="290" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>29</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>949.49774711134114</v>
       </c>
     </row>
-    <row r="291" spans="1:12" ht="21.75" thickBot="1">
+    <row r="291" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>30</v>
       </c>
@@ -11137,7 +11137,7 @@
         <v>935.84662100772891</v>
       </c>
     </row>
-    <row r="292" spans="1:12" ht="21.75" thickBot="1">
+    <row r="292" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>31</v>
       </c>
@@ -11173,7 +11173,7 @@
         <v>937.17887908506532</v>
       </c>
     </row>
-    <row r="293" spans="1:12" ht="21.75" thickBot="1">
+    <row r="293" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>32</v>
       </c>
@@ -11209,7 +11209,7 @@
         <v>884.54305674059947</v>
       </c>
     </row>
-    <row r="294" spans="1:12" ht="21.75" thickBot="1">
+    <row r="294" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>33</v>
       </c>
@@ -11245,7 +11245,7 @@
         <v>939.60807084420389</v>
       </c>
     </row>
-    <row r="295" spans="1:12" ht="21.75" thickBot="1">
+    <row r="295" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>34</v>
       </c>
@@ -11281,7 +11281,7 @@
         <v>931.71341099078131</v>
       </c>
     </row>
-    <row r="296" spans="1:12" ht="21.75" thickBot="1">
+    <row r="296" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>11</v>
       </c>
@@ -11319,7 +11319,7 @@
         <v>463.80709747340745</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="21.75" thickBot="1">
+    <row r="297" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>12</v>
       </c>
@@ -11357,7 +11357,7 @@
         <v>509.779255735893</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="21.75" thickBot="1">
+    <row r="298" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>13</v>
       </c>
@@ -11395,7 +11395,7 @@
         <v>508.43764615948845</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="21.75" thickBot="1">
+    <row r="299" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>14</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>551.58837853897785</v>
       </c>
     </row>
-    <row r="300" spans="1:12" ht="21.75" thickBot="1">
+    <row r="300" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>15</v>
       </c>
@@ -11471,7 +11471,7 @@
         <v>514.80953003884827</v>
       </c>
     </row>
-    <row r="301" spans="1:12" ht="21.75" thickBot="1">
+    <row r="301" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>16</v>
       </c>
@@ -11509,7 +11509,7 @@
         <v>532.64897714174049</v>
       </c>
     </row>
-    <row r="302" spans="1:12" ht="21.75" thickBot="1">
+    <row r="302" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>17</v>
       </c>
@@ -11547,7 +11547,7 @@
         <v>523.4641558791443</v>
       </c>
     </row>
-    <row r="303" spans="1:12" ht="21.75" thickBot="1">
+    <row r="303" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>18</v>
       </c>
@@ -11585,7 +11585,7 @@
         <v>482.35872777761529</v>
       </c>
     </row>
-    <row r="304" spans="1:12" ht="21.75" thickBot="1">
+    <row r="304" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>19</v>
       </c>
@@ -11623,7 +11623,7 @@
         <v>439.37030476884786</v>
       </c>
     </row>
-    <row r="305" spans="1:12" ht="21.75" thickBot="1">
+    <row r="305" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>20</v>
       </c>
@@ -11661,7 +11661,7 @@
         <v>516.92437748568875</v>
       </c>
     </row>
-    <row r="306" spans="1:12" ht="21.75" thickBot="1">
+    <row r="306" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>21</v>
       </c>
@@ -11699,7 +11699,7 @@
         <v>509.64134279991544</v>
       </c>
     </row>
-    <row r="307" spans="1:12" ht="21.75" thickBot="1">
+    <row r="307" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>22</v>
       </c>
@@ -11737,7 +11737,7 @@
         <v>530.58480932894827</v>
       </c>
     </row>
-    <row r="308" spans="1:12" ht="21.75" thickBot="1">
+    <row r="308" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A308" s="2" t="s">
         <v>23</v>
       </c>
@@ -11775,7 +11775,7 @@
         <v>459.45930791816983</v>
       </c>
     </row>
-    <row r="309" spans="1:12" ht="21.75" thickBot="1">
+    <row r="309" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
         <v>24</v>
       </c>
@@ -11813,7 +11813,7 @@
         <v>533.21314653384434</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="21.75" thickBot="1">
+    <row r="310" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A310" s="2" t="s">
         <v>25</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>513.67975035674112</v>
       </c>
     </row>
-    <row r="311" spans="1:12" ht="21.75" thickBot="1">
+    <row r="311" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
         <v>26</v>
       </c>
@@ -11889,7 +11889,7 @@
         <v>483.252629632631</v>
       </c>
     </row>
-    <row r="312" spans="1:12" ht="21.75" thickBot="1">
+    <row r="312" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A312" s="2" t="s">
         <v>27</v>
       </c>
@@ -11927,7 +11927,7 @@
         <v>477.33895611897816</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="21.75" thickBot="1">
+    <row r="313" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A313" s="2" t="s">
         <v>28</v>
       </c>
@@ -11965,7 +11965,7 @@
         <v>534.4577540769003</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="21.75" thickBot="1">
+    <row r="314" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A314" s="2" t="s">
         <v>29</v>
       </c>
@@ -12003,7 +12003,7 @@
         <v>497.7841767466939</v>
       </c>
     </row>
-    <row r="315" spans="1:12" ht="21.75" thickBot="1">
+    <row r="315" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
         <v>30</v>
       </c>
@@ -12041,7 +12041,7 @@
         <v>476.23547691598753</v>
       </c>
     </row>
-    <row r="316" spans="1:12" ht="21.75" thickBot="1">
+    <row r="316" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A316" s="2" t="s">
         <v>31</v>
       </c>
@@ -12079,7 +12079,7 @@
         <v>586.24680398898033</v>
       </c>
     </row>
-    <row r="317" spans="1:12" ht="21.75" thickBot="1">
+    <row r="317" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A317" s="2" t="s">
         <v>32</v>
       </c>
@@ -12117,7 +12117,7 @@
         <v>501.21121229136116</v>
       </c>
     </row>
-    <row r="318" spans="1:12" ht="21.75" thickBot="1">
+    <row r="318" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A318" s="2" t="s">
         <v>33</v>
       </c>
@@ -12155,7 +12155,7 @@
         <v>496.72199126218618</v>
       </c>
     </row>
-    <row r="319" spans="1:12" ht="21.75" thickBot="1">
+    <row r="319" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
         <v>34</v>
       </c>
@@ -12193,7 +12193,7 @@
         <v>500.04382922399441</v>
       </c>
     </row>
-    <row r="320" spans="1:12" ht="21.75" thickBot="1">
+    <row r="320" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A320" s="2" t="s">
         <v>11</v>
       </c>
@@ -12231,7 +12231,7 @@
         <v>566.74544935638801</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="21.75" thickBot="1">
+    <row r="321" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A321" s="2" t="s">
         <v>12</v>
       </c>
@@ -12269,7 +12269,7 @@
         <v>576.60617046693437</v>
       </c>
     </row>
-    <row r="322" spans="1:12" ht="21.75" thickBot="1">
+    <row r="322" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A322" s="2" t="s">
         <v>13</v>
       </c>
@@ -12307,7 +12307,7 @@
         <v>573.43586321035559</v>
       </c>
     </row>
-    <row r="323" spans="1:12" ht="21.75" thickBot="1">
+    <row r="323" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2" t="s">
         <v>14</v>
       </c>
@@ -12345,7 +12345,7 @@
         <v>653.19727488930027</v>
       </c>
     </row>
-    <row r="324" spans="1:12" ht="21.75" thickBot="1">
+    <row r="324" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A324" s="2" t="s">
         <v>15</v>
       </c>
@@ -12383,7 +12383,7 @@
         <v>629.39497758521293</v>
       </c>
     </row>
-    <row r="325" spans="1:12" ht="21.75" thickBot="1">
+    <row r="325" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
         <v>16</v>
       </c>
@@ -12421,7 +12421,7 @@
         <v>612.78758666353565</v>
       </c>
     </row>
-    <row r="326" spans="1:12" ht="21.75" thickBot="1">
+    <row r="326" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A326" s="2" t="s">
         <v>17</v>
       </c>
@@ -12459,7 +12459,7 @@
         <v>605.89072788810847</v>
       </c>
     </row>
-    <row r="327" spans="1:12" ht="21.75" thickBot="1">
+    <row r="327" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A327" s="2" t="s">
         <v>18</v>
       </c>
@@ -12497,7 +12497,7 @@
         <v>588.85241739178355</v>
       </c>
     </row>
-    <row r="328" spans="1:12" ht="21.75" thickBot="1">
+    <row r="328" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A328" s="2" t="s">
         <v>19</v>
       </c>
@@ -12535,7 +12535,7 @@
         <v>522.75458740295301</v>
       </c>
     </row>
-    <row r="329" spans="1:12" ht="21.75" thickBot="1">
+    <row r="329" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A329" s="2" t="s">
         <v>20</v>
       </c>
@@ -12573,7 +12573,7 @@
         <v>613.15124287061303</v>
       </c>
     </row>
-    <row r="330" spans="1:12" ht="21.75" thickBot="1">
+    <row r="330" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A330" s="2" t="s">
         <v>21</v>
       </c>
@@ -12611,7 +12611,7 @@
         <v>587.02109927820663</v>
       </c>
     </row>
-    <row r="331" spans="1:12" ht="21.75" thickBot="1">
+    <row r="331" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A331" s="2" t="s">
         <v>22</v>
       </c>
@@ -12649,7 +12649,7 @@
         <v>599.93244339994055</v>
       </c>
     </row>
-    <row r="332" spans="1:12" ht="21.75" thickBot="1">
+    <row r="332" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A332" s="2" t="s">
         <v>23</v>
       </c>
@@ -12687,7 +12687,7 @@
         <v>558.68589572993187</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="21.75" thickBot="1">
+    <row r="333" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2" t="s">
         <v>24</v>
       </c>
@@ -12725,7 +12725,7 @@
         <v>627.06667651693806</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="21.75" thickBot="1">
+    <row r="334" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A334" s="2" t="s">
         <v>25</v>
       </c>
@@ -12763,7 +12763,7 @@
         <v>611.45429374942137</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="21.75" thickBot="1">
+    <row r="335" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A335" s="2" t="s">
         <v>26</v>
       </c>
@@ -12801,7 +12801,7 @@
         <v>563.18976182615665</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="21.75" thickBot="1">
+    <row r="336" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A336" s="2" t="s">
         <v>27</v>
       </c>
@@ -12839,7 +12839,7 @@
         <v>575.30436674005148</v>
       </c>
     </row>
-    <row r="337" spans="1:12" ht="21.75" thickBot="1">
+    <row r="337" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A337" s="2" t="s">
         <v>28</v>
       </c>
@@ -12877,7 +12877,7 @@
         <v>616.11811371583701</v>
       </c>
     </row>
-    <row r="338" spans="1:12" ht="21.75" thickBot="1">
+    <row r="338" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2" t="s">
         <v>29</v>
       </c>
@@ -12915,7 +12915,7 @@
         <v>596.93188506653473</v>
       </c>
     </row>
-    <row r="339" spans="1:12" ht="21.75" thickBot="1">
+    <row r="339" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A339" s="2" t="s">
         <v>30</v>
       </c>
@@ -12953,7 +12953,7 @@
         <v>590.18565468407382</v>
       </c>
     </row>
-    <row r="340" spans="1:12" ht="21.75" thickBot="1">
+    <row r="340" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2" t="s">
         <v>31</v>
       </c>
@@ -12991,7 +12991,7 @@
         <v>706.34407615246175</v>
       </c>
     </row>
-    <row r="341" spans="1:12" ht="21.75" thickBot="1">
+    <row r="341" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A341" s="2" t="s">
         <v>32</v>
       </c>
@@ -13029,7 +13029,7 @@
         <v>592.99859016404776</v>
       </c>
     </row>
-    <row r="342" spans="1:12" ht="21.75" thickBot="1">
+    <row r="342" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2" t="s">
         <v>33</v>
       </c>
@@ -13067,7 +13067,7 @@
         <v>606.76279053188887</v>
       </c>
     </row>
-    <row r="343" spans="1:12" ht="21.75" thickBot="1">
+    <row r="343" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A343" s="2" t="s">
         <v>34</v>
       </c>
@@ -13105,7 +13105,7 @@
         <v>574.18175871755841</v>
       </c>
     </row>
-    <row r="344" spans="1:12" ht="21.75" thickBot="1">
+    <row r="344" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A344" s="2" t="s">
         <v>11</v>
       </c>
@@ -13143,7 +13143,7 @@
         <v>692.72892451237726</v>
       </c>
     </row>
-    <row r="345" spans="1:12" ht="21.75" thickBot="1">
+    <row r="345" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A345" s="2" t="s">
         <v>12</v>
       </c>
@@ -13181,7 +13181,7 @@
         <v>690.05223140263877</v>
       </c>
     </row>
-    <row r="346" spans="1:12" ht="21.75" thickBot="1">
+    <row r="346" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A346" s="2" t="s">
         <v>13</v>
       </c>
@@ -13219,7 +13219,7 @@
         <v>659.84995327930926</v>
       </c>
     </row>
-    <row r="347" spans="1:12" ht="21.75" thickBot="1">
+    <row r="347" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A347" s="2" t="s">
         <v>14</v>
       </c>
@@ -13257,7 +13257,7 @@
         <v>778.97429287470641</v>
       </c>
     </row>
-    <row r="348" spans="1:12" ht="21.75" thickBot="1">
+    <row r="348" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A348" s="2" t="s">
         <v>15</v>
       </c>
@@ -13295,7 +13295,7 @@
         <v>744.66229222350046</v>
       </c>
     </row>
-    <row r="349" spans="1:12" ht="21.75" thickBot="1">
+    <row r="349" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A349" s="2" t="s">
         <v>16</v>
       </c>
@@ -13333,7 +13333,7 @@
         <v>734.01379882501976</v>
       </c>
     </row>
-    <row r="350" spans="1:12" ht="21.75" thickBot="1">
+    <row r="350" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A350" s="2" t="s">
         <v>17</v>
       </c>
@@ -13371,7 +13371,7 @@
         <v>700.44944026215171</v>
       </c>
     </row>
-    <row r="351" spans="1:12" ht="21.75" thickBot="1">
+    <row r="351" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A351" s="2" t="s">
         <v>18</v>
       </c>
@@ -13409,7 +13409,7 @@
         <v>694.57203953177577</v>
       </c>
     </row>
-    <row r="352" spans="1:12" ht="21.75" thickBot="1">
+    <row r="352" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A352" s="2" t="s">
         <v>19</v>
       </c>
@@ -13447,7 +13447,7 @@
         <v>623.30303403509345</v>
       </c>
     </row>
-    <row r="353" spans="1:12" ht="21.75" thickBot="1">
+    <row r="353" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A353" s="2" t="s">
         <v>20</v>
       </c>
@@ -13485,7 +13485,7 @@
         <v>742.67642450943288</v>
       </c>
     </row>
-    <row r="354" spans="1:12" ht="21.75" thickBot="1">
+    <row r="354" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A354" s="2" t="s">
         <v>21</v>
       </c>
@@ -13523,7 +13523,7 @@
         <v>713.71624957011727</v>
       </c>
     </row>
-    <row r="355" spans="1:12" ht="21.75" thickBot="1">
+    <row r="355" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A355" s="2" t="s">
         <v>22</v>
       </c>
@@ -13561,7 +13561,7 @@
         <v>700.2349286611153</v>
       </c>
     </row>
-    <row r="356" spans="1:12" ht="21.75" thickBot="1">
+    <row r="356" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A356" s="2" t="s">
         <v>23</v>
       </c>
@@ -13599,7 +13599,7 @@
         <v>671.70933884125225</v>
       </c>
     </row>
-    <row r="357" spans="1:12" ht="21.75" thickBot="1">
+    <row r="357" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A357" s="2" t="s">
         <v>24</v>
       </c>
@@ -13637,7 +13637,7 @@
         <v>726.0276277056455</v>
       </c>
     </row>
-    <row r="358" spans="1:12" ht="21.75" thickBot="1">
+    <row r="358" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A358" s="2" t="s">
         <v>25</v>
       </c>
@@ -13675,7 +13675,7 @@
         <v>715.36458078680471</v>
       </c>
     </row>
-    <row r="359" spans="1:12" ht="21.75" thickBot="1">
+    <row r="359" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A359" s="2" t="s">
         <v>26</v>
       </c>
@@ -13713,7 +13713,7 @@
         <v>662.42887396647632</v>
       </c>
     </row>
-    <row r="360" spans="1:12" ht="21.75" thickBot="1">
+    <row r="360" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A360" s="2" t="s">
         <v>27</v>
       </c>
@@ -13751,7 +13751,7 @@
         <v>675.75275278778395</v>
       </c>
     </row>
-    <row r="361" spans="1:12" ht="21.75" thickBot="1">
+    <row r="361" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A361" s="2" t="s">
         <v>28</v>
       </c>
@@ -13789,7 +13789,7 @@
         <v>727.51838703311068</v>
       </c>
     </row>
-    <row r="362" spans="1:12" ht="21.75" thickBot="1">
+    <row r="362" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A362" s="2" t="s">
         <v>29</v>
       </c>
@@ -13827,7 +13827,7 @@
         <v>709.97962129494385</v>
       </c>
     </row>
-    <row r="363" spans="1:12" ht="21.75" thickBot="1">
+    <row r="363" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A363" s="2" t="s">
         <v>30</v>
       </c>
@@ -13865,7 +13865,7 @@
         <v>729.8814090689084</v>
       </c>
     </row>
-    <row r="364" spans="1:12" ht="21.75" thickBot="1">
+    <row r="364" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A364" s="2" t="s">
         <v>31</v>
       </c>
@@ -13903,7 +13903,7 @@
         <v>809.38840633219843</v>
       </c>
     </row>
-    <row r="365" spans="1:12" ht="21.75" thickBot="1">
+    <row r="365" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A365" s="2" t="s">
         <v>32</v>
       </c>
@@ -13941,7 +13941,7 @@
         <v>690.19925219654783</v>
       </c>
     </row>
-    <row r="366" spans="1:12" ht="21.75" thickBot="1">
+    <row r="366" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A366" s="2" t="s">
         <v>33</v>
       </c>
@@ -13979,7 +13979,7 @@
         <v>737.64623648012264</v>
       </c>
     </row>
-    <row r="367" spans="1:12" ht="21.75" thickBot="1">
+    <row r="367" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A367" s="2" t="s">
         <v>34</v>
       </c>
@@ -14017,7 +14017,7 @@
         <v>689.85491217368076</v>
       </c>
     </row>
-    <row r="368" spans="1:12" ht="21.75" thickBot="1">
+    <row r="368" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A368" s="2" t="s">
         <v>11</v>
       </c>
@@ -14055,7 +14055,7 @@
         <v>830.98049475488097</v>
       </c>
     </row>
-    <row r="369" spans="1:12" ht="21.75" thickBot="1">
+    <row r="369" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A369" s="2" t="s">
         <v>12</v>
       </c>
@@ -14093,7 +14093,7 @@
         <v>804.01078592912233</v>
       </c>
     </row>
-    <row r="370" spans="1:12" ht="21.75" thickBot="1">
+    <row r="370" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A370" s="2" t="s">
         <v>13</v>
       </c>
@@ -14131,7 +14131,7 @@
         <v>746.38754264203521</v>
       </c>
     </row>
-    <row r="371" spans="1:12" ht="21.75" thickBot="1">
+    <row r="371" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A371" s="2" t="s">
         <v>14</v>
       </c>
@@ -14169,7 +14169,7 @@
         <v>890.36654613724886</v>
       </c>
     </row>
-    <row r="372" spans="1:12" ht="21.75" thickBot="1">
+    <row r="372" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A372" s="2" t="s">
         <v>15</v>
       </c>
@@ -14207,7 +14207,7 @@
         <v>835.50624614524793</v>
       </c>
     </row>
-    <row r="373" spans="1:12" ht="21.75" thickBot="1">
+    <row r="373" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A373" s="2" t="s">
         <v>16</v>
       </c>
@@ -14245,7 +14245,7 @@
         <v>851.17941800758263</v>
       </c>
     </row>
-    <row r="374" spans="1:12" ht="21.75" thickBot="1">
+    <row r="374" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A374" s="2" t="s">
         <v>17</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>801.19597882857022</v>
       </c>
     </row>
-    <row r="375" spans="1:12" ht="21.75" thickBot="1">
+    <row r="375" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A375" s="2" t="s">
         <v>18</v>
       </c>
@@ -14321,7 +14321,7 @@
         <v>784.81531081690002</v>
       </c>
     </row>
-    <row r="376" spans="1:12" ht="21.75" thickBot="1">
+    <row r="376" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A376" s="2" t="s">
         <v>19</v>
       </c>
@@ -14359,7 +14359,7 @@
         <v>735.87698551271421</v>
       </c>
     </row>
-    <row r="377" spans="1:12" ht="21.75" thickBot="1">
+    <row r="377" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A377" s="2" t="s">
         <v>20</v>
       </c>
@@ -14397,7 +14397,7 @@
         <v>852.93336566207654</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="21.75" thickBot="1">
+    <row r="378" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A378" s="2" t="s">
         <v>21</v>
       </c>
@@ -14435,7 +14435,7 @@
         <v>832.94283613904952</v>
       </c>
     </row>
-    <row r="379" spans="1:12" ht="21.75" thickBot="1">
+    <row r="379" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A379" s="2" t="s">
         <v>22</v>
       </c>
@@ -14473,7 +14473,7 @@
         <v>798.60229387583445</v>
       </c>
     </row>
-    <row r="380" spans="1:12" ht="21.75" thickBot="1">
+    <row r="380" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A380" s="2" t="s">
         <v>23</v>
       </c>
@@ -14511,7 +14511,7 @@
         <v>776.92170121804179</v>
       </c>
     </row>
-    <row r="381" spans="1:12" ht="21.75" thickBot="1">
+    <row r="381" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A381" s="2" t="s">
         <v>24</v>
       </c>
@@ -14549,7 +14549,7 @@
         <v>831.87514703564386</v>
       </c>
     </row>
-    <row r="382" spans="1:12" ht="21.75" thickBot="1">
+    <row r="382" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A382" s="2" t="s">
         <v>25</v>
       </c>
@@ -14587,7 +14587,7 @@
         <v>812.47635595274937</v>
       </c>
     </row>
-    <row r="383" spans="1:12" ht="21.75" thickBot="1">
+    <row r="383" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A383" s="2" t="s">
         <v>26</v>
       </c>
@@ -14625,7 +14625,7 @@
         <v>755.80125209339258</v>
       </c>
     </row>
-    <row r="384" spans="1:12" ht="21.75" thickBot="1">
+    <row r="384" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A384" s="2" t="s">
         <v>36</v>
       </c>
@@ -14663,7 +14663,7 @@
         <v>787.8713690530285</v>
       </c>
     </row>
-    <row r="385" spans="1:12" ht="21.75" thickBot="1">
+    <row r="385" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A385" s="2" t="s">
         <v>28</v>
       </c>
@@ -14701,7 +14701,7 @@
         <v>844.7169206627492</v>
       </c>
     </row>
-    <row r="386" spans="1:12" ht="21.75" thickBot="1">
+    <row r="386" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A386" s="2" t="s">
         <v>29</v>
       </c>
@@ -14739,7 +14739,7 @@
         <v>812.15205466711757</v>
       </c>
     </row>
-    <row r="387" spans="1:12" ht="21.75" thickBot="1">
+    <row r="387" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A387" s="2" t="s">
         <v>30</v>
       </c>
@@ -14777,7 +14777,7 @@
         <v>849.9219944806988</v>
       </c>
     </row>
-    <row r="388" spans="1:12" ht="21.75" thickBot="1">
+    <row r="388" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A388" s="2" t="s">
         <v>31</v>
       </c>
@@ -14815,7 +14815,7 @@
         <v>907.66922530923387</v>
       </c>
     </row>
-    <row r="389" spans="1:12" ht="21.75" thickBot="1">
+    <row r="389" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A389" s="2" t="s">
         <v>32</v>
       </c>
@@ -14853,7 +14853,7 @@
         <v>791.570771709729</v>
       </c>
     </row>
-    <row r="390" spans="1:12" ht="21.75" thickBot="1">
+    <row r="390" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A390" s="2" t="s">
         <v>33</v>
       </c>
@@ -14891,7 +14891,7 @@
         <v>877.52653380324682</v>
       </c>
     </row>
-    <row r="391" spans="1:12" ht="21.75" thickBot="1">
+    <row r="391" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A391" s="2" t="s">
         <v>11</v>
       </c>
@@ -14929,7 +14929,7 @@
         <v>900.06015018671644</v>
       </c>
     </row>
-    <row r="392" spans="1:12" ht="21.75" thickBot="1">
+    <row r="392" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A392" s="2" t="s">
         <v>12</v>
       </c>
@@ -14967,7 +14967,7 @@
         <v>899.53618639035551</v>
       </c>
     </row>
-    <row r="393" spans="1:12" ht="21.75" thickBot="1">
+    <row r="393" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A393" s="2" t="s">
         <v>13</v>
       </c>
@@ -15005,7 +15005,7 @@
         <v>865.41655566009058</v>
       </c>
     </row>
-    <row r="394" spans="1:12" ht="21.75" thickBot="1">
+    <row r="394" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A394" s="2" t="s">
         <v>14</v>
       </c>
@@ -15043,7 +15043,7 @@
         <v>947.98417858338166</v>
       </c>
     </row>
-    <row r="395" spans="1:12" ht="21.75" thickBot="1">
+    <row r="395" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A395" s="2" t="s">
         <v>15</v>
       </c>
@@ -15081,7 +15081,7 @@
         <v>907.88644919026763</v>
       </c>
     </row>
-    <row r="396" spans="1:12" ht="21.75" thickBot="1">
+    <row r="396" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A396" s="2" t="s">
         <v>16</v>
       </c>
@@ -15119,7 +15119,7 @@
         <v>935.39645717663825</v>
       </c>
     </row>
-    <row r="397" spans="1:12" ht="21.75" thickBot="1">
+    <row r="397" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A397" s="2" t="s">
         <v>17</v>
       </c>
@@ -15157,7 +15157,7 @@
         <v>875.67531750753335</v>
       </c>
     </row>
-    <row r="398" spans="1:12" ht="21.75" thickBot="1">
+    <row r="398" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A398" s="2" t="s">
         <v>18</v>
       </c>
@@ -15195,7 +15195,7 @@
         <v>889.26924861181578</v>
       </c>
     </row>
-    <row r="399" spans="1:12" ht="21.75" thickBot="1">
+    <row r="399" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A399" s="2" t="s">
         <v>19</v>
       </c>
@@ -15233,7 +15233,7 @@
         <v>839.8697780532558</v>
       </c>
     </row>
-    <row r="400" spans="1:12" ht="21.75" thickBot="1">
+    <row r="400" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A400" s="2" t="s">
         <v>20</v>
       </c>
@@ -15271,7 +15271,7 @@
         <v>928.66794245953622</v>
       </c>
     </row>
-    <row r="401" spans="1:12" ht="21.75" thickBot="1">
+    <row r="401" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A401" s="2" t="s">
         <v>21</v>
       </c>
@@ -15309,7 +15309,7 @@
         <v>907.37660970512889</v>
       </c>
     </row>
-    <row r="402" spans="1:12" ht="21.75" thickBot="1">
+    <row r="402" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A402" s="2" t="s">
         <v>22</v>
       </c>
@@ -15347,7 +15347,7 @@
         <v>884.43390015507305</v>
       </c>
     </row>
-    <row r="403" spans="1:12" ht="21.75" thickBot="1">
+    <row r="403" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A403" s="2" t="s">
         <v>23</v>
       </c>
@@ -15385,7 +15385,7 @@
         <v>882.26890772932245</v>
       </c>
     </row>
-    <row r="404" spans="1:12" ht="21.75" thickBot="1">
+    <row r="404" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A404" s="2" t="s">
         <v>24</v>
       </c>
@@ -15423,7 +15423,7 @@
         <v>925.31150379664871</v>
       </c>
     </row>
-    <row r="405" spans="1:12" ht="21.75" thickBot="1">
+    <row r="405" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A405" s="2" t="s">
         <v>25</v>
       </c>
@@ -15461,7 +15461,7 @@
         <v>892.93947176521829</v>
       </c>
     </row>
-    <row r="406" spans="1:12" ht="21.75" thickBot="1">
+    <row r="406" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A406" s="2" t="s">
         <v>26</v>
       </c>
@@ -15499,7 +15499,7 @@
         <v>871.41225615260407</v>
       </c>
     </row>
-    <row r="407" spans="1:12" ht="21.75" thickBot="1">
+    <row r="407" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A407" s="2" t="s">
         <v>36</v>
       </c>
@@ -15537,7 +15537,7 @@
         <v>907.48954188362973</v>
       </c>
     </row>
-    <row r="408" spans="1:12" ht="21.75" thickBot="1">
+    <row r="408" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A408" s="2" t="s">
         <v>28</v>
       </c>
@@ -15575,7 +15575,7 @@
         <v>930.12694551196398</v>
       </c>
     </row>
-    <row r="409" spans="1:12" ht="21.75" thickBot="1">
+    <row r="409" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A409" s="2" t="s">
         <v>29</v>
       </c>
@@ -15613,7 +15613,7 @@
         <v>912.51423359104774</v>
       </c>
     </row>
-    <row r="410" spans="1:12" ht="21.75" thickBot="1">
+    <row r="410" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A410" s="2" t="s">
         <v>30</v>
       </c>
@@ -15651,7 +15651,7 @@
         <v>922.81158638187833</v>
       </c>
     </row>
-    <row r="411" spans="1:12" ht="21.75" thickBot="1">
+    <row r="411" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A411" s="2" t="s">
         <v>31</v>
       </c>
@@ -15689,7 +15689,7 @@
         <v>946.89973932344765</v>
       </c>
     </row>
-    <row r="412" spans="1:12" ht="21.75" thickBot="1">
+    <row r="412" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A412" s="2" t="s">
         <v>32</v>
       </c>
@@ -15727,7 +15727,7 @@
         <v>892.16898882730118</v>
       </c>
     </row>
-    <row r="413" spans="1:12" ht="21.75" thickBot="1">
+    <row r="413" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A413" s="2" t="s">
         <v>33</v>
       </c>
@@ -15765,7 +15765,7 @@
         <v>951.63416939257718</v>
       </c>
     </row>
-    <row r="414" spans="1:12" ht="21.75" thickBot="1">
+    <row r="414" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A414" s="2" t="s">
         <v>11</v>
       </c>
@@ -15803,7 +15803,7 @@
         <v>951.4050021346311</v>
       </c>
     </row>
-    <row r="415" spans="1:12" ht="21.75" thickBot="1">
+    <row r="415" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A415" s="2" t="s">
         <v>12</v>
       </c>
@@ -15841,7 +15841,7 @@
         <v>950.26223487419418</v>
       </c>
     </row>
-    <row r="416" spans="1:12" ht="21.75" thickBot="1">
+    <row r="416" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A416" s="2" t="s">
         <v>13</v>
       </c>
@@ -15879,7 +15879,7 @@
         <v>945.57511257410692</v>
       </c>
     </row>
-    <row r="417" spans="1:12" ht="21.75" thickBot="1">
+    <row r="417" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A417" s="2" t="s">
         <v>14</v>
       </c>
@@ -15917,7 +15917,7 @@
         <v>958.08106248593299</v>
       </c>
     </row>
-    <row r="418" spans="1:12" ht="21.75" thickBot="1">
+    <row r="418" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A418" s="2" t="s">
         <v>15</v>
       </c>
@@ -15955,7 +15955,7 @@
         <v>932.24670115978188</v>
       </c>
     </row>
-    <row r="419" spans="1:12" ht="21.75" thickBot="1">
+    <row r="419" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A419" s="2" t="s">
         <v>16</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>960.47570379351782</v>
       </c>
     </row>
-    <row r="420" spans="1:12" ht="21.75" thickBot="1">
+    <row r="420" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A420" s="2" t="s">
         <v>17</v>
       </c>
@@ -16031,7 +16031,7 @@
         <v>942.87789733795705</v>
       </c>
     </row>
-    <row r="421" spans="1:12" ht="21.75" thickBot="1">
+    <row r="421" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A421" s="2" t="s">
         <v>18</v>
       </c>
@@ -16069,7 +16069,7 @@
         <v>951.26975924138196</v>
       </c>
     </row>
-    <row r="422" spans="1:12" ht="21.75" thickBot="1">
+    <row r="422" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A422" s="2" t="s">
         <v>19</v>
       </c>
@@ -16107,7 +16107,7 @@
         <v>905.99265719391019</v>
       </c>
     </row>
-    <row r="423" spans="1:12" ht="21.75" thickBot="1">
+    <row r="423" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A423" s="2" t="s">
         <v>20</v>
       </c>
@@ -16145,7 +16145,7 @@
         <v>963.64315379318668</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="21.75" thickBot="1">
+    <row r="424" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A424" s="2" t="s">
         <v>21</v>
       </c>
@@ -16183,7 +16183,7 @@
         <v>940.32084185981569</v>
       </c>
     </row>
-    <row r="425" spans="1:12" ht="21.75" thickBot="1">
+    <row r="425" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A425" s="2" t="s">
         <v>22</v>
       </c>
@@ -16221,7 +16221,7 @@
         <v>939.96669969735228</v>
       </c>
     </row>
-    <row r="426" spans="1:12" ht="21.75" thickBot="1">
+    <row r="426" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A426" s="2" t="s">
         <v>23</v>
       </c>
@@ -16259,7 +16259,7 @@
         <v>941.72787208537386</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="21.75" thickBot="1">
+    <row r="427" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A427" s="2" t="s">
         <v>24</v>
       </c>
@@ -16297,7 +16297,7 @@
         <v>946.4372944068092</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="21.75" thickBot="1">
+    <row r="428" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A428" s="2" t="s">
         <v>25</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>931.58774764666362</v>
       </c>
     </row>
-    <row r="429" spans="1:12" ht="21.75" thickBot="1">
+    <row r="429" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A429" s="2" t="s">
         <v>26</v>
       </c>
@@ -16373,7 +16373,7 @@
         <v>934.72443821975628</v>
       </c>
     </row>
-    <row r="430" spans="1:12" ht="21.75" thickBot="1">
+    <row r="430" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A430" s="2" t="s">
         <v>36</v>
       </c>
@@ -16411,7 +16411,7 @@
         <v>949.7426522735916</v>
       </c>
     </row>
-    <row r="431" spans="1:12" ht="21.75" thickBot="1">
+    <row r="431" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A431" s="2" t="s">
         <v>28</v>
       </c>
@@ -16449,7 +16449,7 @@
         <v>958.00988452388606</v>
       </c>
     </row>
-    <row r="432" spans="1:12" ht="21.75" thickBot="1">
+    <row r="432" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A432" s="2" t="s">
         <v>29</v>
       </c>
@@ -16487,7 +16487,7 @@
         <v>962.4917694558643</v>
       </c>
     </row>
-    <row r="433" spans="1:12" ht="21.75" thickBot="1">
+    <row r="433" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A433" s="2" t="s">
         <v>30</v>
       </c>
@@ -16525,7 +16525,7 @@
         <v>932.97852229186151</v>
       </c>
     </row>
-    <row r="434" spans="1:12" ht="21.75" thickBot="1">
+    <row r="434" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A434" s="2" t="s">
         <v>31</v>
       </c>
@@ -16563,7 +16563,7 @@
         <v>955.42386619106981</v>
       </c>
     </row>
-    <row r="435" spans="1:12" ht="21.75" thickBot="1">
+    <row r="435" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A435" s="2" t="s">
         <v>32</v>
       </c>
@@ -16601,7 +16601,7 @@
         <v>929.54635706030331</v>
       </c>
     </row>
-    <row r="436" spans="1:12" ht="21.75" thickBot="1">
+    <row r="436" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A436" s="2" t="s">
         <v>33</v>
       </c>
@@ -16639,7 +16639,7 @@
         <v>965.9699484235141</v>
       </c>
     </row>
-    <row r="437" spans="1:12" ht="21.75" thickBot="1">
+    <row r="437" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A437" s="2" t="s">
         <v>11</v>
       </c>
@@ -16677,7 +16677,7 @@
         <v>502.07453393941285</v>
       </c>
     </row>
-    <row r="438" spans="1:12" ht="21.75" thickBot="1">
+    <row r="438" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A438" s="2" t="s">
         <v>12</v>
       </c>
@@ -16715,7 +16715,7 @@
         <v>511.60116045533101</v>
       </c>
     </row>
-    <row r="439" spans="1:12" ht="21.75" thickBot="1">
+    <row r="439" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A439" s="2" t="s">
         <v>13</v>
       </c>
@@ -16753,7 +16753,7 @@
         <v>503.61796203646736</v>
       </c>
     </row>
-    <row r="440" spans="1:12" ht="21.75" thickBot="1">
+    <row r="440" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A440" s="2" t="s">
         <v>14</v>
       </c>
@@ -16791,7 +16791,7 @@
         <v>533.92289224077194</v>
       </c>
     </row>
-    <row r="441" spans="1:12" ht="21.75" thickBot="1">
+    <row r="441" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A441" s="2" t="s">
         <v>15</v>
       </c>
@@ -16829,7 +16829,7 @@
         <v>545.27867055614365</v>
       </c>
     </row>
-    <row r="442" spans="1:12" ht="21.75" thickBot="1">
+    <row r="442" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A442" s="2" t="s">
         <v>16</v>
       </c>
@@ -16867,7 +16867,7 @@
         <v>562.10322404268209</v>
       </c>
     </row>
-    <row r="443" spans="1:12" ht="21.75" thickBot="1">
+    <row r="443" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A443" s="2" t="s">
         <v>17</v>
       </c>
@@ -16905,7 +16905,7 @@
         <v>558.1308873069828</v>
       </c>
     </row>
-    <row r="444" spans="1:12" ht="21.75" thickBot="1">
+    <row r="444" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A444" s="2" t="s">
         <v>18</v>
       </c>
@@ -16943,7 +16943,7 @@
         <v>517.48789212340137</v>
       </c>
     </row>
-    <row r="445" spans="1:12" ht="21.75" thickBot="1">
+    <row r="445" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A445" s="2" t="s">
         <v>19</v>
       </c>
@@ -16981,7 +16981,7 @@
         <v>505.84743511645837</v>
       </c>
     </row>
-    <row r="446" spans="1:12" ht="21.75" thickBot="1">
+    <row r="446" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A446" s="2" t="s">
         <v>20</v>
       </c>
@@ -17019,7 +17019,7 @@
         <v>550.28266251230809</v>
       </c>
     </row>
-    <row r="447" spans="1:12" ht="21.75" thickBot="1">
+    <row r="447" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A447" s="2" t="s">
         <v>21</v>
       </c>
@@ -17057,7 +17057,7 @@
         <v>529.68179119045283</v>
       </c>
     </row>
-    <row r="448" spans="1:12" ht="21.75" thickBot="1">
+    <row r="448" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A448" s="2" t="s">
         <v>22</v>
       </c>
@@ -17095,7 +17095,7 @@
         <v>532.56184782167736</v>
       </c>
     </row>
-    <row r="449" spans="1:12" ht="21.75" thickBot="1">
+    <row r="449" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A449" s="2" t="s">
         <v>23</v>
       </c>
@@ -17133,7 +17133,7 @@
         <v>480.6784166930014</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="21.75" thickBot="1">
+    <row r="450" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A450" s="2" t="s">
         <v>24</v>
       </c>
@@ -17171,7 +17171,7 @@
         <v>543.98432153901274</v>
       </c>
     </row>
-    <row r="451" spans="1:12" ht="21.75" thickBot="1">
+    <row r="451" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A451" s="2" t="s">
         <v>25</v>
       </c>
@@ -17209,7 +17209,7 @@
         <v>546.00776034346279</v>
       </c>
     </row>
-    <row r="452" spans="1:12" ht="21.75" thickBot="1">
+    <row r="452" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A452" s="2" t="s">
         <v>26</v>
       </c>
@@ -17247,7 +17247,7 @@
         <v>489.83314885837763</v>
       </c>
     </row>
-    <row r="453" spans="1:12" ht="21.75" thickBot="1">
+    <row r="453" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A453" s="2" t="s">
         <v>36</v>
       </c>
@@ -17285,7 +17285,7 @@
         <v>505.16240079820818</v>
       </c>
     </row>
-    <row r="454" spans="1:12" ht="21.75" thickBot="1">
+    <row r="454" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A454" s="2" t="s">
         <v>28</v>
       </c>
@@ -17323,7 +17323,7 @@
         <v>545.48323661447216</v>
       </c>
     </row>
-    <row r="455" spans="1:12" ht="21.75" thickBot="1">
+    <row r="455" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A455" s="2" t="s">
         <v>29</v>
       </c>
@@ -17361,7 +17361,7 @@
         <v>563.97398961776582</v>
       </c>
     </row>
-    <row r="456" spans="1:12" ht="21.75" thickBot="1">
+    <row r="456" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A456" s="2" t="s">
         <v>30</v>
       </c>
@@ -17399,7 +17399,7 @@
         <v>528.53933057801714</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="21.75" thickBot="1">
+    <row r="457" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A457" s="2" t="s">
         <v>31</v>
       </c>
@@ -17437,7 +17437,7 @@
         <v>575.02268320609005</v>
       </c>
     </row>
-    <row r="458" spans="1:12" ht="21.75" thickBot="1">
+    <row r="458" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A458" s="2" t="s">
         <v>32</v>
       </c>
@@ -17475,7 +17475,7 @@
         <v>569.66436982429786</v>
       </c>
     </row>
-    <row r="459" spans="1:12" ht="21.75" thickBot="1">
+    <row r="459" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A459" s="2" t="s">
         <v>33</v>
       </c>
@@ -17513,7 +17513,7 @@
         <v>533.91914078875368</v>
       </c>
     </row>
-    <row r="460" spans="1:12" ht="21.75" thickBot="1">
+    <row r="460" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A460" s="2" t="s">
         <v>11</v>
       </c>
@@ -17551,7 +17551,7 @@
         <v>648.00782632690061</v>
       </c>
     </row>
-    <row r="461" spans="1:12" ht="21.75" thickBot="1">
+    <row r="461" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A461" s="2" t="s">
         <v>12</v>
       </c>
@@ -17589,7 +17589,7 @@
         <v>628.32851198215212</v>
       </c>
     </row>
-    <row r="462" spans="1:12" ht="21.75" thickBot="1">
+    <row r="462" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A462" s="2" t="s">
         <v>13</v>
       </c>
@@ -17627,7 +17627,7 @@
         <v>588.05401793859255</v>
       </c>
     </row>
-    <row r="463" spans="1:12" ht="21.75" thickBot="1">
+    <row r="463" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A463" s="2" t="s">
         <v>14</v>
       </c>
@@ -17665,7 +17665,7 @@
         <v>657.29495605487659</v>
       </c>
     </row>
-    <row r="464" spans="1:12" ht="21.75" thickBot="1">
+    <row r="464" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A464" s="2" t="s">
         <v>15</v>
       </c>
@@ -17703,7 +17703,7 @@
         <v>706.90709554655211</v>
       </c>
     </row>
-    <row r="465" spans="1:12" ht="21.75" thickBot="1">
+    <row r="465" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A465" s="2" t="s">
         <v>16</v>
       </c>
@@ -17741,7 +17741,7 @@
         <v>686.76208112808672</v>
       </c>
     </row>
-    <row r="466" spans="1:12" ht="21.75" thickBot="1">
+    <row r="466" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A466" s="2" t="s">
         <v>17</v>
       </c>
@@ -17779,7 +17779,7 @@
         <v>677.07876601091323</v>
       </c>
     </row>
-    <row r="467" spans="1:12" ht="21.75" thickBot="1">
+    <row r="467" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A467" s="2" t="s">
         <v>18</v>
       </c>
@@ -17817,7 +17817,7 @@
         <v>625.3515494476419</v>
       </c>
     </row>
-    <row r="468" spans="1:12" ht="21.75" thickBot="1">
+    <row r="468" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A468" s="2" t="s">
         <v>19</v>
       </c>
@@ -17855,7 +17855,7 @@
         <v>586.08241720454271</v>
       </c>
     </row>
-    <row r="469" spans="1:12" ht="21.75" thickBot="1">
+    <row r="469" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A469" s="2" t="s">
         <v>20</v>
       </c>
@@ -17893,7 +17893,7 @@
         <v>681.30325495046145</v>
       </c>
     </row>
-    <row r="470" spans="1:12" ht="21.75" thickBot="1">
+    <row r="470" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A470" s="2" t="s">
         <v>21</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>663.058686424553</v>
       </c>
     </row>
-    <row r="471" spans="1:12" ht="21.75" thickBot="1">
+    <row r="471" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A471" s="2" t="s">
         <v>22</v>
       </c>
@@ -17969,7 +17969,7 @@
         <v>618.95199493664643</v>
       </c>
     </row>
-    <row r="472" spans="1:12" ht="21.75" thickBot="1">
+    <row r="472" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A472" s="2" t="s">
         <v>23</v>
       </c>
@@ -18007,7 +18007,7 @@
         <v>632.9199094902151</v>
       </c>
     </row>
-    <row r="473" spans="1:12" ht="21.75" thickBot="1">
+    <row r="473" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A473" s="2" t="s">
         <v>24</v>
       </c>
@@ -18045,7 +18045,7 @@
         <v>650.85258606059847</v>
       </c>
     </row>
-    <row r="474" spans="1:12" ht="21.75" thickBot="1">
+    <row r="474" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A474" s="2" t="s">
         <v>25</v>
       </c>
@@ -18083,7 +18083,7 @@
         <v>642.46259076154024</v>
       </c>
     </row>
-    <row r="475" spans="1:12" ht="21.75" thickBot="1">
+    <row r="475" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A475" s="2" t="s">
         <v>26</v>
       </c>
@@ -18121,7 +18121,7 @@
         <v>603.18954724131004</v>
       </c>
     </row>
-    <row r="476" spans="1:12" ht="21.75" thickBot="1">
+    <row r="476" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A476" s="2" t="s">
         <v>36</v>
       </c>
@@ -18159,7 +18159,7 @@
         <v>615.25326304241207</v>
       </c>
     </row>
-    <row r="477" spans="1:12" ht="21.75" thickBot="1">
+    <row r="477" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A477" s="2" t="s">
         <v>28</v>
       </c>
@@ -18197,7 +18197,7 @@
         <v>662.73962920906501</v>
       </c>
     </row>
-    <row r="478" spans="1:12" ht="21.75" thickBot="1">
+    <row r="478" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A478" s="2" t="s">
         <v>29</v>
       </c>
@@ -18235,7 +18235,7 @@
         <v>677.10276112531369</v>
       </c>
     </row>
-    <row r="479" spans="1:12" ht="21.75" thickBot="1">
+    <row r="479" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A479" s="2" t="s">
         <v>30</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>632.6137188530472</v>
       </c>
     </row>
-    <row r="480" spans="1:12" ht="21.75" thickBot="1">
+    <row r="480" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A480" s="2" t="s">
         <v>31</v>
       </c>
@@ -18311,7 +18311,7 @@
         <v>693.4680625348899</v>
       </c>
     </row>
-    <row r="481" spans="1:12" ht="21.75" thickBot="1">
+    <row r="481" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A481" s="2" t="s">
         <v>32</v>
       </c>
@@ -18349,7 +18349,7 @@
         <v>696.44886562223212</v>
       </c>
     </row>
-    <row r="482" spans="1:12" ht="21.75" thickBot="1">
+    <row r="482" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A482" s="2" t="s">
         <v>33</v>
       </c>
@@ -18385,880 +18385,6 @@
       </c>
       <c r="L482">
         <v>655.42104860773566</v>
-      </c>
-    </row>
-    <row r="483" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A483" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B483" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C483" s="3">
-        <v>0.63658344687302104</v>
-      </c>
-      <c r="D483" s="3">
-        <v>0.50069735006973504</v>
-      </c>
-      <c r="E483" s="3">
-        <v>0.8965270735316121</v>
-      </c>
-      <c r="F483" s="3">
-        <v>1</v>
-      </c>
-      <c r="G483" s="3">
-        <v>1</v>
-      </c>
-      <c r="H483" s="2">
-        <v>94.048154761904755</v>
-      </c>
-      <c r="I483" s="2">
-        <v>0</v>
-      </c>
-      <c r="J483" s="2">
-        <v>0</v>
-      </c>
-      <c r="K483" s="2">
-        <v>0</v>
-      </c>
-      <c r="L483">
-        <v>739.2387855490399</v>
-      </c>
-    </row>
-    <row r="484" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A484" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B484" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C484" s="3">
-        <v>0.61638706681372268</v>
-      </c>
-      <c r="D484" s="3">
-        <v>0.82416107382550341</v>
-      </c>
-      <c r="E484" s="3">
-        <v>0.85276761681275448</v>
-      </c>
-      <c r="F484" s="3">
-        <v>0.97029537359545026</v>
-      </c>
-      <c r="G484" s="3">
-        <v>1</v>
-      </c>
-      <c r="H484" s="2">
-        <v>93.453144654088064</v>
-      </c>
-      <c r="I484" s="2">
-        <v>0</v>
-      </c>
-      <c r="J484" s="2">
-        <v>0</v>
-      </c>
-      <c r="K484" s="2">
-        <v>0</v>
-      </c>
-      <c r="L484">
-        <v>756.91167614373092</v>
-      </c>
-    </row>
-    <row r="485" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A485" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B485" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C485" s="3">
-        <v>0.46732694819329562</v>
-      </c>
-      <c r="D485" s="3">
-        <v>0.80182529335071706</v>
-      </c>
-      <c r="E485" s="3">
-        <v>0.83527190212475599</v>
-      </c>
-      <c r="F485" s="3">
-        <v>1</v>
-      </c>
-      <c r="G485" s="3">
-        <v>1</v>
-      </c>
-      <c r="H485" s="2">
-        <v>93.469828571428579</v>
-      </c>
-      <c r="I485" s="2">
-        <v>0</v>
-      </c>
-      <c r="J485" s="2">
-        <v>0</v>
-      </c>
-      <c r="K485" s="2">
-        <v>0</v>
-      </c>
-      <c r="L485">
-        <v>675.68217941281284</v>
-      </c>
-    </row>
-    <row r="486" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A486" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B486" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C486" s="3">
-        <v>0.5955747689424592</v>
-      </c>
-      <c r="D486" s="3">
-        <v>0.9507658643326039</v>
-      </c>
-      <c r="E486" s="3">
-        <v>0.93012147557602098</v>
-      </c>
-      <c r="F486" s="3">
-        <v>0.96932129011944812</v>
-      </c>
-      <c r="G486" s="3">
-        <v>1</v>
-      </c>
-      <c r="H486" s="2">
-        <v>91.751047619047625</v>
-      </c>
-      <c r="I486" s="2">
-        <v>0</v>
-      </c>
-      <c r="J486" s="2">
-        <v>0</v>
-      </c>
-      <c r="K486" s="2">
-        <v>0</v>
-      </c>
-      <c r="L486">
-        <v>761.32588598260543</v>
-      </c>
-    </row>
-    <row r="487" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A487" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B487" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C487" s="3">
-        <v>0.69724194974473064</v>
-      </c>
-      <c r="D487" s="3">
-        <v>0.75722543352601157</v>
-      </c>
-      <c r="E487" s="3">
-        <v>0.88337310380092038</v>
-      </c>
-      <c r="F487" s="3">
-        <v>0.96975421610878243</v>
-      </c>
-      <c r="G487" s="3">
-        <v>1</v>
-      </c>
-      <c r="H487" s="2">
-        <v>94.468015873015872</v>
-      </c>
-      <c r="I487" s="2">
-        <v>0</v>
-      </c>
-      <c r="J487" s="2">
-        <v>0</v>
-      </c>
-      <c r="K487" s="2">
-        <v>0</v>
-      </c>
-      <c r="L487">
-        <v>795.64905319609716</v>
-      </c>
-    </row>
-    <row r="488" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A488" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B488" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C488" s="3">
-        <v>0.66732265305494909</v>
-      </c>
-      <c r="D488" s="3">
-        <v>0.93119266055045868</v>
-      </c>
-      <c r="E488" s="3">
-        <v>0.88974955311665094</v>
-      </c>
-      <c r="F488" s="3">
-        <v>0.98404077375681365</v>
-      </c>
-      <c r="G488" s="3">
-        <v>1</v>
-      </c>
-      <c r="H488" s="2">
-        <v>95.278993439550135</v>
-      </c>
-      <c r="I488" s="2">
-        <v>0</v>
-      </c>
-      <c r="J488" s="2">
-        <v>0</v>
-      </c>
-      <c r="K488" s="2">
-        <v>0</v>
-      </c>
-      <c r="L488">
-        <v>798.82979605049945</v>
-      </c>
-    </row>
-    <row r="489" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A489" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B489" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C489" s="3">
-        <v>0.60495956232159853</v>
-      </c>
-      <c r="D489" s="3">
-        <v>0.97972116603295312</v>
-      </c>
-      <c r="E489" s="3">
-        <v>0.88161926778130206</v>
-      </c>
-      <c r="F489" s="3">
-        <v>1</v>
-      </c>
-      <c r="G489" s="3">
-        <v>1</v>
-      </c>
-      <c r="H489" s="2">
-        <v>92.008005050505048</v>
-      </c>
-      <c r="I489" s="2">
-        <v>0</v>
-      </c>
-      <c r="J489" s="2">
-        <v>0</v>
-      </c>
-      <c r="K489" s="2">
-        <v>0</v>
-      </c>
-      <c r="L489">
-        <v>767.70788093067949</v>
-      </c>
-    </row>
-    <row r="490" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A490" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B490" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C490" s="3">
-        <v>0.56338172941025311</v>
-      </c>
-      <c r="D490" s="3">
-        <v>0.64660361134995703</v>
-      </c>
-      <c r="E490" s="3">
-        <v>0.91625336842436378</v>
-      </c>
-      <c r="F490" s="3">
-        <v>1</v>
-      </c>
-      <c r="G490" s="3">
-        <v>1</v>
-      </c>
-      <c r="H490" s="2">
-        <v>94.506847732912263</v>
-      </c>
-      <c r="I490" s="2">
-        <v>0</v>
-      </c>
-      <c r="J490" s="2">
-        <v>0</v>
-      </c>
-      <c r="K490" s="2">
-        <v>0</v>
-      </c>
-      <c r="L490">
-        <v>719.02716004354716</v>
-      </c>
-    </row>
-    <row r="491" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A491" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B491" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C491" s="3">
-        <v>0.66998320196407801</v>
-      </c>
-      <c r="D491" s="3">
-        <v>0.97677554689841173</v>
-      </c>
-      <c r="E491" s="3">
-        <v>0.87425746443645458</v>
-      </c>
-      <c r="F491" s="3">
-        <v>0.82201822224846011</v>
-      </c>
-      <c r="G491" s="3">
-        <v>1</v>
-      </c>
-      <c r="H491" s="2">
-        <v>94.122692307692319</v>
-      </c>
-      <c r="I491" s="2">
-        <v>0</v>
-      </c>
-      <c r="J491" s="2">
-        <v>0</v>
-      </c>
-      <c r="K491" s="2">
-        <v>0</v>
-      </c>
-      <c r="L491">
-        <v>787.49283030262234</v>
-      </c>
-    </row>
-    <row r="492" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A492" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B492" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C492" s="3">
-        <v>0.65873542515878281</v>
-      </c>
-      <c r="D492" s="3">
-        <v>0.81663326653306612</v>
-      </c>
-      <c r="E492" s="3">
-        <v>0.90626420183835921</v>
-      </c>
-      <c r="F492" s="3">
-        <v>1</v>
-      </c>
-      <c r="G492" s="3">
-        <v>1</v>
-      </c>
-      <c r="H492" s="2">
-        <v>95.198210526315791</v>
-      </c>
-      <c r="I492" s="2">
-        <v>0</v>
-      </c>
-      <c r="J492" s="2">
-        <v>0</v>
-      </c>
-      <c r="K492" s="2">
-        <v>0</v>
-      </c>
-      <c r="L492">
-        <v>789.16602101695298</v>
-      </c>
-    </row>
-    <row r="493" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A493" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B493" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C493" s="3">
-        <v>0.72343080345033361</v>
-      </c>
-      <c r="D493" s="3">
-        <v>0.76859504132231404</v>
-      </c>
-      <c r="E493" s="3">
-        <v>0.87019810508182605</v>
-      </c>
-      <c r="F493" s="3">
-        <v>0.88674065765393462</v>
-      </c>
-      <c r="G493" s="3">
-        <v>1</v>
-      </c>
-      <c r="H493" s="2">
-        <v>94.36881127450981</v>
-      </c>
-      <c r="I493" s="2">
-        <v>0</v>
-      </c>
-      <c r="J493" s="2">
-        <v>0</v>
-      </c>
-      <c r="K493" s="2">
-        <v>0</v>
-      </c>
-      <c r="L493">
-        <v>802.78932306981812</v>
-      </c>
-    </row>
-    <row r="494" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A494" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B494" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C494" s="3">
-        <v>0.53258814369925478</v>
-      </c>
-      <c r="D494" s="3">
-        <v>0.98730606488011285</v>
-      </c>
-      <c r="E494" s="3">
-        <v>0.89117577478116872</v>
-      </c>
-      <c r="F494" s="3">
-        <v>0.95882283487809195</v>
-      </c>
-      <c r="G494" s="3">
-        <v>1</v>
-      </c>
-      <c r="H494" s="2">
-        <v>91.067296703296705</v>
-      </c>
-      <c r="I494" s="2">
-        <v>0</v>
-      </c>
-      <c r="J494" s="2">
-        <v>0</v>
-      </c>
-      <c r="K494" s="2">
-        <v>0</v>
-      </c>
-      <c r="L494">
-        <v>723.6036657137073</v>
-      </c>
-    </row>
-    <row r="495" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A495" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B495" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C495" s="3">
-        <v>0.57665180650741898</v>
-      </c>
-      <c r="D495" s="3">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E495" s="3">
-        <v>0.82778047390964915</v>
-      </c>
-      <c r="F495" s="3">
-        <v>0.94799968514473509</v>
-      </c>
-      <c r="G495" s="3">
-        <v>1</v>
-      </c>
-      <c r="H495" s="2">
-        <v>93.791785714285709</v>
-      </c>
-      <c r="I495" s="2">
-        <v>0</v>
-      </c>
-      <c r="J495" s="2">
-        <v>0</v>
-      </c>
-      <c r="K495" s="2">
-        <v>0</v>
-      </c>
-      <c r="L495">
-        <v>729.91691447450626</v>
-      </c>
-    </row>
-    <row r="496" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A496" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B496" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C496" s="3">
-        <v>0.58646425023561477</v>
-      </c>
-      <c r="D496" s="3">
-        <v>0.98324022346368711</v>
-      </c>
-      <c r="E496" s="3">
-        <v>0.8422972393076813</v>
-      </c>
-      <c r="F496" s="3">
-        <v>0.99064289509416137</v>
-      </c>
-      <c r="G496" s="3">
-        <v>1</v>
-      </c>
-      <c r="H496" s="2">
-        <v>94.215483476132192</v>
-      </c>
-      <c r="I496" s="2">
-        <v>0</v>
-      </c>
-      <c r="J496" s="2">
-        <v>0</v>
-      </c>
-      <c r="K496" s="2">
-        <v>0</v>
-      </c>
-      <c r="L496">
-        <v>759.15913296150529</v>
-      </c>
-    </row>
-    <row r="497" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A497" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B497" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C497" s="3">
-        <v>0.58158640656025951</v>
-      </c>
-      <c r="D497" s="3">
-        <v>0.78628783199505869</v>
-      </c>
-      <c r="E497" s="3">
-        <v>0.88365782140710658</v>
-      </c>
-      <c r="F497" s="3">
-        <v>1</v>
-      </c>
-      <c r="G497" s="3">
-        <v>1</v>
-      </c>
-      <c r="H497" s="2">
-        <v>93.346366497773701</v>
-      </c>
-      <c r="I497" s="2">
-        <v>0</v>
-      </c>
-      <c r="J497" s="2">
-        <v>0</v>
-      </c>
-      <c r="K497" s="2">
-        <v>0</v>
-      </c>
-      <c r="L497">
-        <v>736.84767330542229</v>
-      </c>
-    </row>
-    <row r="498" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A498" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B498" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C498" s="3">
-        <v>0.57241106979499157</v>
-      </c>
-      <c r="D498" s="3">
-        <v>0.73469387755102045</v>
-      </c>
-      <c r="E498" s="3">
-        <v>0.85382239382239378</v>
-      </c>
-      <c r="F498" s="3">
-        <v>0.85448767144853088</v>
-      </c>
-      <c r="G498" s="3">
-        <v>1</v>
-      </c>
-      <c r="H498" s="2">
-        <v>93.730243612596553</v>
-      </c>
-      <c r="I498" s="2">
-        <v>0</v>
-      </c>
-      <c r="J498" s="2">
-        <v>0</v>
-      </c>
-      <c r="K498" s="2">
-        <v>0</v>
-      </c>
-      <c r="L498">
-        <v>712.47448689979706</v>
-      </c>
-    </row>
-    <row r="499" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A499" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B499" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C499" s="3">
-        <v>0.59172325558508021</v>
-      </c>
-      <c r="D499" s="3">
-        <v>0.5440084835630965</v>
-      </c>
-      <c r="E499" s="3">
-        <v>0.90351217457801813</v>
-      </c>
-      <c r="F499" s="3">
-        <v>0.99025326170376049</v>
-      </c>
-      <c r="G499" s="3">
-        <v>1</v>
-      </c>
-      <c r="H499" s="2">
-        <v>93.052376512376526</v>
-      </c>
-      <c r="I499" s="2">
-        <v>0</v>
-      </c>
-      <c r="J499" s="2">
-        <v>0</v>
-      </c>
-      <c r="K499" s="2">
-        <v>0</v>
-      </c>
-      <c r="L499">
-        <v>721.92634161085641</v>
-      </c>
-    </row>
-    <row r="500" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A500" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B500" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C500" s="3">
-        <v>0.59607755310980293</v>
-      </c>
-      <c r="D500" s="3">
-        <v>0.99151515151515146</v>
-      </c>
-      <c r="E500" s="3">
-        <v>0.92358745259368769</v>
-      </c>
-      <c r="F500" s="3">
-        <v>0.98090206033414007</v>
-      </c>
-      <c r="G500" s="3">
-        <v>1</v>
-      </c>
-      <c r="H500" s="2">
-        <v>95.070461538461558</v>
-      </c>
-      <c r="I500" s="2">
-        <v>0</v>
-      </c>
-      <c r="J500" s="2">
-        <v>0</v>
-      </c>
-      <c r="K500" s="2">
-        <v>0</v>
-      </c>
-      <c r="L500">
-        <v>770.15483693378235</v>
-      </c>
-    </row>
-    <row r="501" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A501" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B501" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C501" s="3">
-        <v>0.64417485758139259</v>
-      </c>
-      <c r="D501" s="3">
-        <v>0.76046176046176051</v>
-      </c>
-      <c r="E501" s="3">
-        <v>0.90755190430358856</v>
-      </c>
-      <c r="F501" s="3">
-        <v>1</v>
-      </c>
-      <c r="G501" s="3">
-        <v>1</v>
-      </c>
-      <c r="H501" s="2">
-        <v>93.478823529411756</v>
-      </c>
-      <c r="I501" s="2">
-        <v>0</v>
-      </c>
-      <c r="J501" s="2">
-        <v>0</v>
-      </c>
-      <c r="K501" s="2">
-        <v>0</v>
-      </c>
-      <c r="L501">
-        <v>773.82117124535375</v>
-      </c>
-    </row>
-    <row r="502" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A502" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B502" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C502" s="3">
-        <v>0.65561549513405082</v>
-      </c>
-      <c r="D502" s="3">
-        <v>0.65217391304347827</v>
-      </c>
-      <c r="E502" s="3">
-        <v>0.83344466246399196</v>
-      </c>
-      <c r="F502" s="3">
-        <v>0.96964598461144891</v>
-      </c>
-      <c r="G502" s="3">
-        <v>1</v>
-      </c>
-      <c r="H502" s="2">
-        <v>94.145151515151539</v>
-      </c>
-      <c r="I502" s="2">
-        <v>0</v>
-      </c>
-      <c r="J502" s="2">
-        <v>0</v>
-      </c>
-      <c r="K502" s="2">
-        <v>0</v>
-      </c>
-      <c r="L502">
-        <v>761.91566360437218</v>
-      </c>
-    </row>
-    <row r="503" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A503" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B503" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C503" s="3">
-        <v>0.6977652098676852</v>
-      </c>
-      <c r="D503" s="3">
-        <v>0.96630434782608698</v>
-      </c>
-      <c r="E503" s="3">
-        <v>0.91436630376829542</v>
-      </c>
-      <c r="F503" s="3">
-        <v>1</v>
-      </c>
-      <c r="G503" s="3">
-        <v>1</v>
-      </c>
-      <c r="H503" s="2">
-        <v>94.12929919137467</v>
-      </c>
-      <c r="I503" s="2">
-        <v>0</v>
-      </c>
-      <c r="J503" s="2">
-        <v>0</v>
-      </c>
-      <c r="K503" s="2">
-        <v>0</v>
-      </c>
-      <c r="L503">
-        <v>824.53059940121022</v>
-      </c>
-    </row>
-    <row r="504" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A504" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B504" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C504" s="3">
-        <v>0.66230352448902952</v>
-      </c>
-      <c r="D504" s="3">
-        <v>0.84455324357405137</v>
-      </c>
-      <c r="E504" s="3">
-        <v>0.78376641084576726</v>
-      </c>
-      <c r="F504" s="3">
-        <v>1</v>
-      </c>
-      <c r="G504" s="3">
-        <v>1</v>
-      </c>
-      <c r="H504" s="2">
-        <v>95.209137931034476</v>
-      </c>
-      <c r="I504" s="2">
-        <v>0</v>
-      </c>
-      <c r="J504" s="2">
-        <v>0</v>
-      </c>
-      <c r="K504" s="2">
-        <v>0</v>
-      </c>
-      <c r="L504">
-        <v>783.93140075740587</v>
-      </c>
-    </row>
-    <row r="505" spans="1:12" ht="21.75" thickBot="1">
-      <c r="A505" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B505" s="4">
-        <v>46266</v>
-      </c>
-      <c r="C505" s="3">
-        <v>0.69580386006465444</v>
-      </c>
-      <c r="D505" s="3">
-        <v>0.70313901345291485</v>
-      </c>
-      <c r="E505" s="3">
-        <v>0.9281189503663988</v>
-      </c>
-      <c r="F505" s="3">
-        <v>1</v>
-      </c>
-      <c r="G505" s="3">
-        <v>1</v>
-      </c>
-      <c r="H505" s="2">
-        <v>94.700742240215931</v>
-      </c>
-      <c r="I505" s="2">
-        <v>0</v>
-      </c>
-      <c r="J505" s="2">
-        <v>0</v>
-      </c>
-      <c r="K505" s="2">
-        <v>0</v>
-      </c>
-      <c r="L505">
-        <v>797.70676662106735</v>
       </c>
     </row>
   </sheetData>
